--- a/public/exports-with-coowners/29189803.xlsx
+++ b/public/exports-with-coowners/29189803.xlsx
@@ -14464,12 +14464,12 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311041324</t>
+          <t xml:space="preserve">311041311</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319330</t>
+          <t xml:space="preserve">311319327</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -19789,7 +19789,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624659</t>
+          <t xml:space="preserve">311624658</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -26764,7 +26764,7 @@
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759941</t>
+          <t xml:space="preserve">311759970</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -26839,7 +26839,7 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759941</t>
+          <t xml:space="preserve">311759970</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">

--- a/public/exports-with-coowners/29189803.xlsx
+++ b/public/exports-with-coowners/29189803.xlsx
@@ -26764,7 +26764,7 @@
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759970</t>
+          <t xml:space="preserve">311759941</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -26839,7 +26839,7 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759970</t>
+          <t xml:space="preserve">311759941</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
